--- a/www/download/COUNTRY.CYP.rpO1.xlsx
+++ b/www/download/COUNTRY.CYP.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Chipre</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.772678123777948</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.796685775755041</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.877292976582033</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.883384436593682</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.926586570603177</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.06079414511591</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.09817702407959</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.03987932720202</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.882706029234349</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.799673759926997</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.792091754634952</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.783471856320399</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.727151112510703</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.679902076410497</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948682306625</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>2.57589525050955</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>2.49130245109944</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.40538065852176</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>2.40511312921354</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>2.54910209541684</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>2.49188147941359</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>2.39113066803107</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>2.46837172760578</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>2.75858867508923</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>2.47389501453645</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>2.47726236539441</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>2.45809659232384</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>2.41069060564864</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>2.42841272433425</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>2.35416667555386</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>4.04583380548295</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>3.91342090347299</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>3.73570435018472</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>3.65329977420272</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>3.80349198428458</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>3.70943784742365</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>3.58537733366708</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>3.64291109591663</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>3.88430511391483</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>3.69308744262681</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>3.7348723027549</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>3.66507309838528</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>3.55611519259192</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>3.40675977577921</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>3.33135865676762</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>556.844</t>
+          <t>4.63769935620284</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>559.558</t>
+          <t>4.45126249273082</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>565.864</t>
+          <t>4.24928487828574</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>576.508</t>
+          <t>4.13225107426169</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>590.902</t>
+          <t>4.26700599823759</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>605.96</t>
+          <t>4.20252124610983</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>626.986</t>
+          <t>4.08989219442423</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>631.03</t>
+          <t>4.17898913672983</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>652.422</t>
+          <t>3.64810458586566</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>663.882</t>
+          <t>4.16230303964564</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>679.879</t>
+          <t>4.15135733724456</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>694.745</t>
+          <t>4.0201102978184</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>715.064</t>
+          <t>4.00813841350074</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>724.744</t>
+          <t>3.71799126831701</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>725.571</t>
+          <t>3.59263552013344</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>385.082</t>
+          <t>296762977290.803</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>388.735</t>
+          <t>274388097928.136</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>393.173</t>
+          <t>272857063851.275</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>400.651</t>
+          <t>311345771067.213</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>410.296</t>
+          <t>338127425608.22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>421.155</t>
+          <t>357760130582.843</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>433.872</t>
+          <t>382982284108.93</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>443.031</t>
+          <t>414006174206.577</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>455.955</t>
+          <t>509067818002.756</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>458.638</t>
+          <t>492024405734.744</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>473.113</t>
+          <t>469545228210.605</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>494.479</t>
+          <t>435307133173.646</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>516.413</t>
+          <t>374741169410.785</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>540.57</t>
+          <t>336571962183.328</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>541.705</t>
+          <t>307785271811.902</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>71936418024.3562</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>66171507744.0884</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>65856933199.2303</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>76325604758.0028</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>82558825687.0731</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>87967089401.2113</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>96737564388.6956</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>106044326595.754</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>131513923083.861</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>127228514989.476</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>121158385540.791</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>111927859519.754</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>96996924587.6467</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>83754868283.7115</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>78274066285.4785</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>1012278661.8147</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>917311089.220526</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>953095370.347778</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>1048652658.35322</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>1127172736.67091</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>1265835823.15372</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>1316653381.37629</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>1284338457.11879</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>1239220308.8392</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>1061664003.90299</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>910107474.563246</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>797912035.488227</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>584469037.932671</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39.55</t>
+          <t>455074556.66012</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>418715444.846846</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>8383.27165302559</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>8680.40168968542</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>8558.39858316071</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>9040.54892969407</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>9125.7137515814</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>8478.1924729092</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>8620.50931253793</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>9715.06369884756</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>12865.4033829614</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>15193.6631891568</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>16029.7780852351</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>17319.498655498</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>19883.916082431</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>23330.6609799445</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>23805.1741724101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>13341.4789525891</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>13855.4286762487</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>13488.6769903916</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>13967.8097853572</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>14139.9825717788</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>13191.5896537208</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>13353.2138846032</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>15092.0785409474</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>19498.641928414</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>22651.1076583971</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>24196.8231484183</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>26021.100349962</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29873.1612337792</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>35746.5819477757</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>34033.1560755415</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.58</t>
+          <t>2.94961087668958</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>1801.60642508965</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>1885.24202254569</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>1842.95376845835</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>1995.49941526408</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>1973.87655566176</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>1885.15426599401</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>1902.78882302786</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>2218.23423176032</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>2577.0655686432</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>2939.68158238706</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>2989.28895231551</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>3334.34051158918</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>3862.56328610428</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>4674.07128540555</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.772678123777948</t>
+          <t>321551.6940292</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.796685775755041</t>
+          <t>292875.730979898</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.877292976582033</t>
+          <t>287882.653918952</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.883384436593682</t>
+          <t>327175.371146776</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.926586570603177</t>
+          <t>346910.525300148</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.06079414511591</t>
+          <t>363951.549032732</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.09817702407959</t>
+          <t>389756.504386364</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.03987932720202</t>
+          <t>414883.906869145</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.882706029234349</t>
+          <t>500243.146001754</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.799673759926997</t>
+          <t>464507.174112728</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.792091754634952</t>
+          <t>423927.171241395</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.783471856320399</t>
+          <t>378006.955487179</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.727151112510703</t>
+          <t>314109.211747561</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902076410497</t>
+          <t>256444.789601076</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948682306625</t>
+          <t>240547.222758078</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-992794428.018386</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-3265675928.8615</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-4289690560.26679</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-1440862385.96451</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>332733747.23831</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-1017009439.08932</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-275396891.010248</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3548169694.44818</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-2020530469.59571</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7539555020.91026</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>15503823598.0677</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4733399679.72787</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2790296285.96434</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>4658929748.75214</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>14139823766.4783</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-565250591.484403</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-1093638411.49009</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-1178325933.29464</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-181874907.605236</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>544472322.882798</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2060592848.25261</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1033530178.51866</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2875350463.18497</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1350520092.77147</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>106026097.47621</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2819577103.72061</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-5856660255.48275</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-3179684928.95771</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-1532003196.20439</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>6365227608.93807</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-427543836.533983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-2172037517.37141</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-3111364626.97215</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-1258987478.35927</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>-211738575.644488</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-3077602287.34193</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>-1308927069.52891</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>672819231.263211</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-3371050562.36718</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>7433528923.43406</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>18323400701.7883</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>10590059935.2106</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>5969981214.92205</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>6190932944.95653</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7774596157.5402</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1441348.27827489</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1273857.97379969</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1219838.95122775</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1378870.20445329</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1508065.09270374</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1551145.53616263</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1616413.46388127</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1745056.4561401</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2163076.3277831</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1950335.89538258</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1792013.51288366</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1565916.73903012</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1272299.11225754</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1012857.13027878</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>930107.464486208</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1454225.65065428</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1346099.43998178</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1365768.85041003</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1578442.45095055</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1720302.08563804</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1851865.20805881</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2015413.82240785</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2136928.90568544</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2566381.92537174</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2452356.99011685</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>2283254.73500491</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2078089.94198459</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1734540.67003197</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1482034.563787</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1381026.32548905</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>257.59</t>
+          <t>1986.75605591144</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>249.13</t>
+          <t>2113.1513598131</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>240.54</t>
+          <t>2064.14002772178</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>240.51</t>
+          <t>2082.82920060218</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>254.91</t>
+          <t>2162.24533912994</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>249.19</t>
+          <t>2147.15485544231</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>239.11</t>
+          <t>2290.77504501028</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>246.84</t>
+          <t>2299.08485759001</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>275.86</t>
+          <t>2752.51981074515</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>247.39</t>
+          <t>3347.5841392997</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>247.73</t>
+          <t>3450.0903690429</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>245.81</t>
+          <t>3796.76966358804</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>241.07</t>
+          <t>4611.57890213568</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>242.84</t>
+          <t>5147.43092485272</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>235.42</t>
+          <t>4628.49509079995</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>404.58</t>
+          <t>50488948220.895</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>391.34</t>
+          <t>49587313095.4001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>373.57</t>
+          <t>51719417742.5691</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>365.33</t>
+          <t>55902811814.3402</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>380.35</t>
+          <t>61808546773.7808</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>370.94</t>
+          <t>67705337197.152</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>358.54</t>
+          <t>75148534647.8236</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>364.29</t>
+          <t>74395895684.0784</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>388.43</t>
+          <t>87384522848.5888</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>369.31</t>
+          <t>78072971516.4084</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>373.49</t>
+          <t>57318185919.4213</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>366.51</t>
+          <t>65530448889.8528</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>355.61</t>
+          <t>59930656255.5132</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>340.68</t>
+          <t>46205975287.7358</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>333.14</t>
+          <t>37814791016.5211</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>463.77</t>
+          <t>3903.81993369891</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>445.13</t>
+          <t>4188.43247851129</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>424.93</t>
+          <t>4019.55139186513</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>413.23</t>
+          <t>4033.88415550994</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>426.7</t>
+          <t>4092.21245558792</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>420.25</t>
+          <t>4242.13096642063</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>408.99</t>
+          <t>4402.20095822659</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>417.9</t>
+          <t>4735.10396469906</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>364.81</t>
+          <t>5495.71255800651</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>416.23</t>
+          <t>6384.3116209553</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>415.14</t>
+          <t>6664.35606501167</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>402.01</t>
+          <t>7593.47009763796</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>400.81</t>
+          <t>9632.78411611902</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>371.8</t>
+          <t>11415.8392821631</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>359.26</t>
+          <t>8671.10649166191</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>430596.215</t>
+          <t>119463126809.599</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>400733.803</t>
+          <t>113861234694.627</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>409047.771</t>
+          <t>112614613867.636</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>480004.349</t>
+          <t>127629057008.089</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>532949.586</t>
+          <t>140067941528.305</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>582967.167</t>
+          <t>162016950205.081</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>648761.709</t>
+          <t>178190525419.353</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>701553.76</t>
+          <t>192863833072.233</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>874622.96</t>
+          <t>207262071734.921</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>866417.725</t>
+          <t>196299746700.668</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>836584.535</t>
+          <t>176976467248.003</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>773880.694</t>
+          <t>175151536477.524</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>666930.888</t>
+          <t>164855259312.788</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>579722.526</t>
+          <t>145107786262.136</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>542208.509</t>
+          <t>111760273380.832</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>322453.385</t>
+          <t>-1917.06387778747</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>287811.839</t>
+          <t>-2075.28111869819</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>279054.161</t>
+          <t>-1955.41136414335</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>321671.836</t>
+          <t>-1951.05495490776</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>358893.934</t>
+          <t>-1929.96711645797</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>374911.876</t>
+          <t>-2094.97611097832</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>401193.822</t>
+          <t>-2111.42591321631</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>446036.43</t>
+          <t>-2436.01910710905</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>568672.767</t>
+          <t>-2743.19274726135</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>534197.002</t>
+          <t>-3036.7274816556</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>512157.462</t>
+          <t>-3214.26569596877</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>463667.946</t>
+          <t>-3796.70043404992</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>392885.966</t>
+          <t>-5021.20521398334</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>330799.139</t>
+          <t>-6268.4083573104</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>302656.969</t>
+          <t>-4042.61140086197</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>296762.977</t>
+          <t>-68974178588.7037</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>274388.098</t>
+          <t>-64273921599.2269</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>272857.064</t>
+          <t>-60895196125.0666</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>311345.771</t>
+          <t>-71726245193.7489</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>338127.426</t>
+          <t>-78259394754.5242</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>357760.131</t>
+          <t>-94311613007.9293</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>382982.284</t>
+          <t>-103041990771.529</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>414006.174</t>
+          <t>-118467937388.155</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>509067.818</t>
+          <t>-119877548886.332</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>492024.406</t>
+          <t>-118226775184.259</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>469545.228</t>
+          <t>-119658281328.582</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>435307.133</t>
+          <t>-109621087587.672</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>374741.169</t>
+          <t>-104924603057.275</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>336571.962</t>
+          <t>-98901810974.4005</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>307785.272</t>
+          <t>-73945482364.3105</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>3289.33855</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>3301.17601</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>3070.01195</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>3277.96135</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>3227.9768</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2970.60471</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>3048.41562</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3366.44822</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>4252.8315</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>4995.28712</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>5266.43538</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>5524.38471</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>6331.55874</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>7278.69535</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>6796.58128</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>186474.428</t>
+          <t>0.0375187785128083</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>171903.661</t>
+          <t>0.0341515113624229</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>173124.429</t>
+          <t>0.032030009690466</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201515.966</t>
+          <t>0.0388912941557167</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>218221.917</t>
+          <t>0.0431555061880204</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>229931.292</t>
+          <t>0.0443602917796223</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>247244.025</t>
+          <t>0.0461548987236938</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>266503.805</t>
+          <t>0.0352635423620661</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>335888.153</t>
+          <t>0.0324377934266696</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>330034.77</t>
+          <t>0.035519351409085</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>311061.736</t>
+          <t>0.0367211643522404</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>289737.99</t>
+          <t>0.0362572743582257</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>249431.987</t>
+          <t>0.0419947262059996</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>219669.851</t>
+          <t>0.0388144924550873</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>215286.587</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4009.30204461226</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4110.62893189141</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3985.18004554325</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4160.21885548685</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4226.76494684178</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3977.86902232336</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>4095.1821265542</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4664.52482765077</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6094.95444184257</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>7135.12399070072</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>7639.76272830467</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>8245.92046224411</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>9545.39955151358</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>11024.2451353322</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>10604.365021569</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>71936.418</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>66171.508</t>
+          <t>5428.85074392709</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65856.933</t>
+          <t>5270.72917188927</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>76325.605</t>
+          <t>5483.52170324111</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>82558.826</t>
+          <t>5598.45614178127</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>87967.089</t>
+          <t>5290.57706587232</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>96737.564</t>
+          <t>5477.72397844922</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>106044.327</t>
+          <t>6144.2804408705</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>131513.923</t>
+          <t>8016.30446858495</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>127228.515</t>
+          <t>9440.96012703077</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>121158.386</t>
+          <t>10170.0773856905</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>111927.86</t>
+          <t>10905.9669471042</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>96996.925</t>
+          <t>12486.3005746237</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>83754.868</t>
+          <t>14467.4037383969</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>78274.066</t>
+          <t>13817.1416338568</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>36529.8037857805</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>37487.7032509869</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>35563.213394576</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>36751.9667967827</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>36265.9523848064</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>32633.2348156165</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>33016.6545840697</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>36533.9452894855</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>45002.8512596556</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>53359.7893934907</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>57946.9071727335</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>62627.0932247143</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>72474.0691091171</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.96</t>
+          <t>86099.5392394877</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1012.279</t>
+          <t>5284.91893755531</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>917.311</t>
+          <t>5455.39135868644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>953.095</t>
+          <t>5645.12988085847</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1048.653</t>
+          <t>5745.15417948743</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1127.173</t>
+          <t>6005.84982413465</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1265.836</t>
+          <t>6349.97905401159</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1316.653</t>
+          <t>6647.25188224167</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1284.338</t>
+          <t>7098.23950453184</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1239.22</t>
+          <t>7575.489937585</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1061.664</t>
+          <t>8045.80011186733</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>910.107</t>
+          <t>8497.11821011226</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>797.912</t>
+          <t>8705.03496547207</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>584.469</t>
+          <t>8949.51823133714</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>455.075</t>
+          <t>9176.45124006597</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>418.715</t>
+          <t>9087.11431011384</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4009.30204461226</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4126.86311251552</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4270.32832980622</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4369.6860878491</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4512.5640103078</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4742.11401089715</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4921.84600579111</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5363.73180868011</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5738.08342482409</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6066.29332678926</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6391.84905601753</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6596.88058665277</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6858.45153611619</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>7047.65434601301</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7008.56538602621</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3172.16004244469</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3165.50374607291</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2982.04383811073</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3424.83096675889</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3538.95208821873</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3332.77408412768</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3426.66917155078</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3506.5505591295</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4036.85876141505</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4834.98669296923</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5117.16685430948</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5605.02821289582</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>6906.09197537635</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>8015.98120160314</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>7436.5410161432</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>322453385225.373</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>287811839158.296</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>279054160545.019</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>321671835715.515</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>358893933833.707</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>374911876090.507</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>401193821735.331</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>446036430189.409</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>568672766574.176</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>534197001745.29</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>512157461982.151</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>463667946426.819</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>392885965865.128</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>330799138749.05</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>302656968943.812</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>430596215158.732</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>400733803282.576</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>409047770697.803</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>480004349334.062</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>532949586130.666</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>582967167496.915</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>648761709433.087</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>701553759736.531</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>874622960166.689</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>866417724608.284</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>836584534905.798</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>773880694395.06</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>666930887627.291</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>579722526433.309</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>542208508993.083</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>186474427912.406</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>171903660618.448</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>173124429499.912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>201515965683.985</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>218221916611.003</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>229931291514.888</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>247244024938.809</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>266503804841.754</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>335888153233.149</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>330034769792.258</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>311061735791.919</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>289737989797.985</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>249431987022.87</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>219669851414.774</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>215286586613.414</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>297700</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>299500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>304100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>309800</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>314800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>321900</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>328300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>340800</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>353300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>366400</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>372400</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>384500</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>391166.670871672</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>392612.725033373</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>223716.495232719</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>225937.149256762</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>228763.11685584</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>233286.523036485</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>237983.052303308</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>241700</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>248200</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>255600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>262900</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>273900</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>285800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>296100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>308800</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>326600</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>325400</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>556844000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>559558000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>565864000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>576508000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>590902000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>605960000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>626986000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>631030000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>652422000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>663882000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>679879000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>694745000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>715064000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>724744333.122296</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>725571484.03977</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>385081830.189556</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>388735218.183415</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>393173063.331875</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>400650693.290692</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>410295651.543646</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>421155000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>433872000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>443031000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>455955000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>458638000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>473113000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>494479000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>516413000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>540570000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>541705000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.390116927880701</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.384904366830866</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.369970763777891</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.352881576519591</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.353397642917275</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.358280413431593</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.353910440875485</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.358248084348114</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.339631106733564</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.364859725162261</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.347331262498627</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.353356172580841</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.36971202850082</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.361581828929178</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.361957673459242</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.321293200762932</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.328626938735117</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.322348896331952</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.315242186789605</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.337233876652075</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.342979664793355</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.349594082475155</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.348925892107897</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.338509157324964</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.365575717545096</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.379463226115965</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.387763044649832</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.383128728066806</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.395468700852395</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.399773244605587</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.288589871356368</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.286468694434018</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.307680339890158</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.331876236690805</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.30936848043065</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.298739921775052</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.296495476649359</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.292826023543989</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.321859735941472</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.269564557292643</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.273205511385408</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.258880782769327</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.247159243432374</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.242949470218427</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.238269081935171</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.29501632942481</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.293308740062344</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.280608690472955</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.267314716451038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.267813512574648</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.271519071909591</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.271893085468395</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.278524698977206</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.280286225135778</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.279550377287939</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.265568736297898</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.274163910756846</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.293637463282541</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.302300726860568</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.302163821283627</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.359447173559755</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.367002576026058</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.358082664819624</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.347848501886329</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.371520788571168</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.377445256022587</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.382594963330836</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.380685901781172</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.390437025126417</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.403575019887614</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.416900756395004</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.428554835823112</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.420868018826323</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.425813446969654</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.429346185139048</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.345536497015435</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.339688683911597</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.361308644707421</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.384836781662633</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.360665698854184</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.351035672067821</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.345511951200769</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.340789399241622</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.329276749737806</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.316874602824447</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.317530507307097</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.297281253420042</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.285494517891135</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.271885826169778</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.268489993577326</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13745.56817</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14025.103</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>13541.08615</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>14456.44642</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>14904.16569</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>14176.64369</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14825.93409</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>16295.25573</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20252.26861</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>23628.63618</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>25577.21377</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>28109.62515</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>33700.83554</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>40127.54318</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>37463.21071</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>8457.07898</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8594.35449</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8252.77301</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8908.35267</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9137.40823</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>8623.35115</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8904.39315</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9650.831</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>12053.16323</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>14275.94682</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>15287.24424</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>16510.99516</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>19392.39255</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>22483.38494</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>21253.68265</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>28225.7804786168</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28703.0313879198</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29087.669044844</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>29535.6804326495</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>29943.9567213731</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>30381.0747399953</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30840.3990575789</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>31403.4282774735</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>31951.0194714376</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>32656.6168437408</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33395.9865417147</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>34307.1617116782</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>35470.9755419079</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>36716.5888590675</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
